--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0002T0006Z000C1N142_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0002T0006Z000C1N142_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>46.31387933544549</v>
+        <v>7.526005392009893</v>
       </c>
       <c r="D2" t="n">
-        <v>17.66906588663756</v>
+        <v>2.871223206578603</v>
       </c>
       <c r="E2" t="n">
-        <v>5.054694908091359</v>
+        <v>0.8213879225648458</v>
       </c>
       <c r="F2" t="n">
-        <v>11.55177052649816</v>
+        <v>1.877162710555952</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>51.80359244717134</v>
+        <v>8.418083772665343</v>
       </c>
       <c r="D3" t="n">
-        <v>9.222660894231115</v>
+        <v>1.498682395312556</v>
       </c>
       <c r="E3" t="n">
-        <v>5.054694908091359</v>
+        <v>0.8213879225648458</v>
       </c>
       <c r="F3" t="n">
-        <v>11.55177052649816</v>
+        <v>1.877162710555952</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>41.54641052313448</v>
+        <v>6.751291710009354</v>
       </c>
       <c r="D4" t="n">
-        <v>33.506632842535</v>
+        <v>5.444827836911937</v>
       </c>
       <c r="E4" t="n">
-        <v>5.054694908091359</v>
+        <v>0.8213879225648458</v>
       </c>
       <c r="F4" t="n">
-        <v>11.55177052649816</v>
+        <v>1.877162710555952</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>42.05964593147201</v>
+        <v>6.834692463864203</v>
       </c>
       <c r="D5" t="n">
-        <v>42.96921266097795</v>
+        <v>6.982497057408917</v>
       </c>
       <c r="E5" t="n">
-        <v>5.054694908091359</v>
+        <v>0.8213879225648458</v>
       </c>
       <c r="F5" t="n">
-        <v>11.55177052649816</v>
+        <v>1.877162710555952</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>34.89458643438344</v>
+        <v>5.670370295587309</v>
       </c>
       <c r="D6" t="n">
-        <v>35.17403449866265</v>
+        <v>5.715780606032681</v>
       </c>
       <c r="E6" t="n">
-        <v>5.054694908091359</v>
+        <v>0.8213879225648458</v>
       </c>
       <c r="F6" t="n">
-        <v>11.55177052649816</v>
+        <v>1.877162710555952</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>41.42552727977071</v>
+        <v>6.73164818296274</v>
       </c>
       <c r="D7" t="n">
-        <v>40.35308000515491</v>
+        <v>6.557375500837674</v>
       </c>
       <c r="E7" t="n">
-        <v>5.054694908091359</v>
+        <v>0.8213879225648458</v>
       </c>
       <c r="F7" t="n">
-        <v>11.55177052649816</v>
+        <v>1.877162710555952</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>38.27552120569585</v>
+        <v>6.219772195925576</v>
       </c>
       <c r="D8" t="n">
-        <v>36.30586084006205</v>
+        <v>5.899702386510083</v>
       </c>
       <c r="E8" t="n">
-        <v>5.054694908091359</v>
+        <v>0.8213879225648458</v>
       </c>
       <c r="F8" t="n">
-        <v>11.55177052649816</v>
+        <v>1.877162710555952</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
